--- a/public/template/Contoh Format Arsip.xlsx
+++ b/public/template/Contoh Format Arsip.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AA020E-B5AE-44D2-A1B3-70D72B063900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BE606F-D90B-4F01-8F66-90D7DCA043D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>kode_klasifikasi</t>
   </si>
@@ -64,12 +64,6 @@
   </si>
   <si>
     <t>nomor_box</t>
-  </si>
-  <si>
-    <t>aktif</t>
-  </si>
-  <si>
-    <t>inaktif</t>
   </si>
   <si>
     <t>keterangan_jra</t>
@@ -89,17 +83,20 @@
     <t>5 TAHUN</t>
   </si>
   <si>
-    <t>RT. 01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Laporan Barang Milik Negara Tingkat Wilayah Semester 1 Tahun Anggaran 2014 KPU Provinsi Bali
 </t>
   </si>
   <si>
-    <t>Laporan Pertanggungjawaban dan Laporan Posisi Anggaran dan Kas (LPJ/LPAK) Bagian Anggaran 076 Bulan September 2012</t>
-  </si>
-  <si>
     <t>Sub Bagian Keuangan</t>
+  </si>
+  <si>
+    <t>Laporan BMNN</t>
+  </si>
+  <si>
+    <t>aktif_tahun</t>
+  </si>
+  <si>
+    <t>inaktif_tahun</t>
   </si>
 </sst>
 </file>
@@ -132,6 +129,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -233,15 +231,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -262,6 +254,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,7 +555,7 @@
     <col min="12" max="12" width="24.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,26 +584,26 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="52" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
+      <c r="A2" s="12" t="s">
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="13">
         <v>2014</v>
       </c>
       <c r="E2" s="4">
@@ -617,33 +615,33 @@
       <c r="G2" s="6">
         <v>21</v>
       </c>
-      <c r="H2" s="7">
-        <v>0.8847222222222223</v>
+      <c r="H2" s="15">
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" ht="39" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="16">
+      <c r="B3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="14">
         <v>2010</v>
       </c>
       <c r="E3" s="5">
@@ -652,23 +650,23 @@
       <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>22</v>
       </c>
-      <c r="H3" s="9">
-        <v>0.92638888888888893</v>
+      <c r="H3" s="16">
+        <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>18</v>
+      <c r="J3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/template/Contoh Format Arsip.xlsx
+++ b/public/template/Contoh Format Arsip.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkCentre-Umum2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BE606F-D90B-4F01-8F66-90D7DCA043D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9735"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$2</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>kode_klasifikasi</t>
   </si>
@@ -36,61 +38,61 @@
     <t>sub_bagian</t>
   </si>
   <si>
+    <t>jumlah_berkas</t>
+  </si>
+  <si>
+    <t>keterangan</t>
+  </si>
+  <si>
+    <t>tanggal_arsip</t>
+  </si>
+  <si>
+    <t>nomor_rak</t>
+  </si>
+  <si>
+    <t>nomor_box</t>
+  </si>
+  <si>
+    <t>keterangan_jra</t>
+  </si>
+  <si>
+    <t>Pemberitahuan KPU Provinsi Bali perihal Tata cara Pencoblosan Gambar Pasangan Calon yang Tembus di Lipatan Bagian Lain, Sempanjang Tidak Mengenai Gambar Pasangan Calon Lain di Anggap Sah</t>
+  </si>
+  <si>
+    <t>1 BENDEL</t>
+  </si>
+  <si>
+    <t>MUSNAH</t>
+  </si>
+  <si>
+    <t>Sub Bagian Teknis Penyelenggaraan Pemilu</t>
+  </si>
+  <si>
+    <t>2 TAHUN</t>
+  </si>
+  <si>
+    <t>3 TAHUN</t>
+  </si>
+  <si>
+    <t>link_foto</t>
+  </si>
+  <si>
+    <t>nomor_sampul</t>
+  </si>
+  <si>
+    <t>Arda</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1XEq6oPdL3c2eWqVSOcAN5zS-XCVFKqSr</t>
+  </si>
+  <si>
+    <t>TEKSTUAL/BAIK</t>
+  </si>
+  <si>
+    <t>PP.06.1</t>
+  </si>
+  <si>
     <t>tahun_arsip</t>
-  </si>
-  <si>
-    <t>jumlah_berkas</t>
-  </si>
-  <si>
-    <t>keterangan</t>
-  </si>
-  <si>
-    <t>KU.03.2</t>
-  </si>
-  <si>
-    <t>Sub Bagian Umum dan Logistik</t>
-  </si>
-  <si>
-    <t>1 Lembar</t>
-  </si>
-  <si>
-    <t>Tekstual/Baik</t>
-  </si>
-  <si>
-    <t>tanggal_arsip</t>
-  </si>
-  <si>
-    <t>nomor_rak</t>
-  </si>
-  <si>
-    <t>nomor_box</t>
-  </si>
-  <si>
-    <t>keterangan_jra</t>
-  </si>
-  <si>
-    <t>1 Tahun Setelah
-Barang Tidak
-Dikuasai</t>
-  </si>
-  <si>
-    <t>2 TAHUN</t>
-  </si>
-  <si>
-    <t>MUSNAH</t>
-  </si>
-  <si>
-    <t>5 TAHUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laporan Barang Milik Negara Tingkat Wilayah Semester 1 Tahun Anggaran 2014 KPU Provinsi Bali
-</t>
-  </si>
-  <si>
-    <t>Sub Bagian Keuangan</t>
-  </si>
-  <si>
-    <t>Laporan BMNN</t>
   </si>
   <si>
     <t>aktif_tahun</t>
@@ -102,8 +104,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,25 +122,38 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Roboto"/>
-      <charset val="1"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +169,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -182,90 +203,89 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FFF8F9FA"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -540,137 +560,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.453125" customWidth="1"/>
-    <col min="2" max="2" width="42.453125" customWidth="1"/>
-    <col min="3" max="3" width="31.1796875" customWidth="1"/>
-    <col min="4" max="5" width="17.453125" customWidth="1"/>
-    <col min="6" max="8" width="19.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.7265625" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" customWidth="1"/>
-    <col min="11" max="11" width="19.1796875" customWidth="1"/>
-    <col min="12" max="12" width="24.08984375" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="114.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="50.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="26.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="14" customFormat="1" ht="30">
+      <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2004</v>
+      </c>
+      <c r="E2" s="11">
+        <v>38352</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="5">
+        <v>24</v>
+      </c>
+      <c r="I2" s="5">
+        <v>3</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="L2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="52" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="13">
-        <v>2014</v>
-      </c>
-      <c r="E2" s="4">
-        <v>41858</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="6">
-        <v>21</v>
-      </c>
-      <c r="H2" s="15">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>16</v>
-      </c>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1">
+      <c r="E3" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="14">
-        <v>2010</v>
-      </c>
-      <c r="E3" s="5">
-        <v>40451</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="7">
-        <v>22</v>
-      </c>
-      <c r="H3" s="16">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>16</v>
-      </c>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1">
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N2"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B2 D2 F2">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>$L2="BELUM TERIDENTIFIKASI"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="N2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/template/Contoh Format Arsip.xlsx
+++ b/public/template/Contoh Format Arsip.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkCentre-Umum2\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkCentre-Umum2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$2</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>kode_klasifikasi</t>
   </si>
@@ -56,9 +56,6 @@
     <t>keterangan_jra</t>
   </si>
   <si>
-    <t>Pemberitahuan KPU Provinsi Bali perihal Tata cara Pencoblosan Gambar Pasangan Calon yang Tembus di Lipatan Bagian Lain, Sempanjang Tidak Mengenai Gambar Pasangan Calon Lain di Anggap Sah</t>
-  </si>
-  <si>
     <t>1 BENDEL</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>nomor_sampul</t>
   </si>
   <si>
-    <t>Arda</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1XEq6oPdL3c2eWqVSOcAN5zS-XCVFKqSr</t>
   </si>
   <si>
@@ -99,13 +93,49 @@
   </si>
   <si>
     <t>inaktif_tahun</t>
+  </si>
+  <si>
+    <t>klasifikasi_keamanan</t>
+  </si>
+  <si>
+    <t>TERBATAS</t>
+  </si>
+  <si>
+    <t>tingkat_perkembangan</t>
+  </si>
+  <si>
+    <t>asli</t>
+  </si>
+  <si>
+    <t>Copy</t>
+  </si>
+  <si>
+    <t>lokasi_arsip</t>
+  </si>
+  <si>
+    <t>Record Center Inaktif</t>
+  </si>
+  <si>
+    <t>Record Center Permanen</t>
+  </si>
+  <si>
+    <t>Biasa/Terbuka</t>
+  </si>
+  <si>
+    <t>Laporan Pelaksanaan Kegiatan Fasilitasi Pendidikan Pemilih dalam Pemilu 2014</t>
+  </si>
+  <si>
+    <t>PL.01.6</t>
+  </si>
+  <si>
+    <t>Surat Dinas Nomor: 1448/UND/X/2013 perihal Undangan Rapat Pleno Penetapan Zona Pemasangan Alat Peraga Kampanye Dalam Pemilu Anggota DPR DPD dan DPRD Tahun 2013 Di Provinsi Bali</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,19 +143,6 @@
       <family val="2"/>
       <charset val="1"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Roboto"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -140,20 +157,44 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF434343"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,12 +204,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,24 +244,24 @@
       <right style="medium">
         <color rgb="FFFFFFFF"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFF8F9FA"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFF8F9FA"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -236,47 +271,77 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -561,78 +626,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="114.42578125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="114.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
     <col min="5" max="5" width="28.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
-    <col min="11" max="11" width="50.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="26.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="31.7109375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="72" customWidth="1"/>
+    <col min="6" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" customWidth="1"/>
+    <col min="14" max="14" width="50.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="31.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" s="7" customFormat="1" ht="15.75">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>15</v>
+      <c r="Q1" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="14" customFormat="1" ht="30">
-      <c r="A2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>12</v>
+    <row r="2" spans="1:17" s="13" customFormat="1" ht="31.5">
+      <c r="A2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="10">
         <v>2004</v>
@@ -641,51 +717,116 @@
         <v>38352</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="8">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8">
+        <v>2</v>
+      </c>
+      <c r="J2" s="8">
+        <v>3</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="Q2" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="13" customFormat="1" ht="31.5">
+      <c r="A3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2004</v>
+      </c>
+      <c r="E3" s="11">
+        <v>38352</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8">
+        <v>3</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5">
-        <v>24</v>
-      </c>
-      <c r="I2" s="5">
-        <v>3</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="N3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>18</v>
+      <c r="P3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1">
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" thickBot="1">
+    <row r="4" spans="1:17" ht="15.75" thickBot="1">
       <c r="E4" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B2 D2 F2">
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>$L2="BELUM TERIDENTIFIKASI"</formula>
+  <autoFilter ref="A1:Q2"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B2 D2:D3 F2:G3">
+    <cfRule type="expression" dxfId="3" priority="11">
+      <formula>$O2="BELUM TERIDENTIFIKASI"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$H3="BELUM TERIDENTIFIKASI"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
+    <hyperlink ref="Q2" r:id="rId1"/>
+    <hyperlink ref="Q3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>